--- a/output/pdf_financials_xlsx/HEVI.xlsx
+++ b/output/pdf_financials_xlsx/HEVI.xlsx
@@ -629,19 +629,19 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>1.412</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>7.363</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>2.953</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>1.391</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>3.901</v>
       </c>
     </row>
     <row r="11">
@@ -651,13 +651,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0</v>
+        <v>-1.412</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>-7.363</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-2.953</v>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.172</v>
+        <v>-3.729</v>
       </c>
     </row>
     <row r="12">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">

--- a/output/pdf_financials_xlsx/HEVI.xlsx
+++ b/output/pdf_financials_xlsx/HEVI.xlsx
@@ -1984,19 +1984,19 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="71">
@@ -2006,19 +2006,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>0.016</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
     </row>
     <row r="72">
@@ -2094,19 +2094,19 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>12.316</v>
+        <v>12.3</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2160,19 +2160,19 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="79">
@@ -2182,19 +2182,19 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>0.022</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="80">
@@ -2203,30 +2203,20 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.02904929577464789</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.002266333229134104</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.00399368440605554</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.002269210933470861</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.001890855612164505</v>
       </c>
     </row>
     <row r="81">
@@ -2324,19 +2314,19 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>0.043</v>
+        <v>0.034</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>0.143</v>
+        <v>0.121</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>0.152</v>
+        <v>0.15</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.491</v>
+        <v>0.478</v>
       </c>
     </row>
     <row r="86">
@@ -2865,13 +2855,13 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.008999999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -4034,7 +4024,11 @@
           <t>Lease obligations (note 8)</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -4108,7 +4102,11 @@
           <t>Lease obligations (note 8)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -4800,7 +4798,11 @@
           <t>Lease obligations (note 9)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
         <v>0.016</v>
       </c>
@@ -4837,7 +4839,11 @@
           <t>Lease obligations (note 9)</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
         <v>0.017</v>
       </c>
@@ -5465,7 +5471,11 @@
           <t>Accretion (note 9)</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -7109,7 +7119,11 @@
           <t>Accretion (note 10)</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
